--- a/FM-MN-07_BENDING-01.xlsx
+++ b/FM-MN-07_BENDING-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6395B6-E539-4B46-B7A3-D454C2D2BF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9513481D-7274-4C88-9B05-48AB30FF38E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43F5B061-2B5D-4206-8D9C-5E7A9B8E5457}"/>
   </bookViews>
@@ -361,11 +361,41 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -373,37 +403,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1457,80 +1459,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="26" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
     </row>
     <row r="2" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="26" t="s">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26"/>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="26"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
     </row>
     <row r="3" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="18"/>
@@ -1568,49 +1570,49 @@
       <c r="AG3" s="16"/>
     </row>
     <row r="4" spans="1:33" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
     </row>
     <row r="5" spans="1:33" s="8" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="9">
         <v>1</v>
       </c>
@@ -2059,169 +2061,144 @@
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="20"/>
-      <c r="AF16" s="20"/>
-      <c r="AG16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="21"/>
+      <c r="AC16" s="21"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="21"/>
+      <c r="AF16" s="21"/>
+      <c r="AG16" s="21"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="5"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="19"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="29"/>
+      <c r="AG17" s="29"/>
     </row>
     <row r="18" spans="2:33" ht="22.5" customHeight="1">
       <c r="B18" s="5"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
-      <c r="AE18" s="20"/>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="21"/>
+      <c r="AB18" s="21"/>
+      <c r="AC18" s="21"/>
+      <c r="AD18" s="21"/>
+      <c r="AE18" s="21"/>
+      <c r="AF18" s="21"/>
+      <c r="AG18" s="21"/>
     </row>
     <row r="19" spans="2:33" ht="19.5" customHeight="1">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="33"/>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="33"/>
     </row>
     <row r="20" spans="2:33" ht="246" customHeight="1">
       <c r="B20" s="33"/>
@@ -2250,122 +2227,73 @@
       <c r="Y20" s="33"/>
       <c r="Z20" s="33"/>
       <c r="AA20" s="33"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="33"/>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="33"/>
     </row>
-    <row r="21" spans="2:33" ht="23.25" customHeight="1">
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33"/>
-    </row>
+    <row r="21" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="22" spans="2:33" ht="23.25" customHeight="1">
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="33"/>
       <c r="AB22" s="4"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
+      <c r="AG22" s="32"/>
     </row>
     <row r="23" spans="2:33" ht="23.25" customHeight="1">
-      <c r="AC23" s="21" t="s">
+      <c r="AC23" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AD23" s="21"/>
-      <c r="AE23" s="21"/>
-      <c r="AF23" s="21"/>
-      <c r="AG23" s="21"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
     </row>
     <row r="24" spans="2:33" ht="7.5" customHeight="1">
       <c r="D24" s="3"/>
     </row>
     <row r="25" spans="2:33" ht="14.25" customHeight="1">
       <c r="C25" s="2"/>
-      <c r="AC25" s="23" t="s">
+      <c r="AC25" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="AD25" s="23"/>
-      <c r="AE25" s="23"/>
-      <c r="AF25" s="23"/>
-      <c r="AG25" s="23"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="U15:U16"/>
+  <mergeCells count="72">
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="AG17:AG18"/>
+    <mergeCell ref="AC23:AG23"/>
+    <mergeCell ref="AC17:AC18"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="B20:AG20"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="AC25:AG25"/>
+    <mergeCell ref="AD17:AD18"/>
+    <mergeCell ref="AE17:AE18"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="AF17:AF18"/>
+    <mergeCell ref="AB15:AB16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="J17:J18"/>
@@ -2382,32 +2310,35 @@
     <mergeCell ref="N15:N16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="I15:I16"/>
-    <mergeCell ref="AC15:AC16"/>
-    <mergeCell ref="AD15:AD16"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="AF17:AF18"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="AC25:AG25"/>
-    <mergeCell ref="AD17:AD18"/>
-    <mergeCell ref="AE17:AE18"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="AG17:AG18"/>
-    <mergeCell ref="AC23:AG23"/>
-    <mergeCell ref="AC17:AC18"/>
-    <mergeCell ref="AC22:AG22"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
